--- a/examples/excel/charts/charts-boxwhisker.xlsx
+++ b/examples/excel/charts/charts-boxwhisker.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Basics &amp; Quartile" sheetId="2" r:id="R3b40ca46bc184339"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Axes &amp; Styling" sheetId="3" r:id="R9ef6650a7bdf489a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Basics &amp; Quartile" sheetId="2" r:id="R6e7b8729df494311"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Axes &amp; Styling" sheetId="3" r:id="R83e9e6de01bd499f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -34,7 +34,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R33a2da6fccc444c7"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R3d3c9965afad436f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -64,7 +64,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R368195fa13724721"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R55d9378830ab4a7f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -94,7 +94,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Recb70e81afe347fb"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R37502c420d954a2e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -124,7 +124,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R1831e29045b043f1"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rf5600bbcee084cf9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -159,7 +159,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R7212500ffa1f44be"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R58a028bf4a494e46"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -189,7 +189,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R2222f36f3ec545de"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R3405555e72cb4d8d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -219,7 +219,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R3949504b61b44072"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R45b2cc1a7a4e4499"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -249,7 +249,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R1fa3422874c44dd7"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R5ce74d0029de4289"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -324,7 +324,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{48E7EAA5-17C6-48B1-BC62-04FAB68DDBD1}">
+        <cx:series layoutId="boxWhisker" uniqueId="{E11A4EA2-EEE1-4C2B-B103-433D6092FA47}">
           <cx:tx>
             <cx:txData>
               <cx:f>1-Basics &amp; Quartile!$B$1</cx:f>
@@ -487,7 +487,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{A1AC5EC2-9457-4CCF-B4F5-B7BB35C191C9}">
+        <cx:series layoutId="boxWhisker" uniqueId="{4571C092-7490-4E64-A0A5-28694D5DD6E9}">
           <cx:tx>
             <cx:txData>
               <cx:f>1-Basics &amp; Quartile!$B$1</cx:f>
@@ -500,7 +500,7 @@
             <cx:statistics quartileMethod="inclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{6A16FC0A-CD83-47C5-BBC0-EC2653902AB4}">
+        <cx:series layoutId="boxWhisker" uniqueId="{1A323AD5-9288-4424-A2BD-3729C6C0B6C3}">
           <cx:tx>
             <cx:txData>
               <cx:f>1-Basics &amp; Quartile!$C$1</cx:f>
@@ -513,7 +513,7 @@
             <cx:statistics quartileMethod="inclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{DF161513-1CBE-4D67-B86E-9757ABFD8700}">
+        <cx:series layoutId="boxWhisker" uniqueId="{05DFEABB-75AB-4448-804C-76D4E8984BE1}">
           <cx:tx>
             <cx:txData>
               <cx:f>1-Basics &amp; Quartile!$D$1</cx:f>
@@ -597,8 +597,6 @@
                 <a:solidFill>
                   <a:srgbClr val="1B2838"/>
                 </a:solidFill>
-                <a:latin typeface="Georgia"/>
-                <a:ea typeface="Georgia"/>
                 <a:effectLst>
                   <a:outerShdw blurRad="76200" dist="38100" dir="2700000" algn="tl" rotWithShape="0">
                     <a:srgbClr val="000000">
@@ -606,6 +604,8 @@
                     </a:srgbClr>
                   </a:outerShdw>
                 </a:effectLst>
+                <a:latin typeface="Georgia"/>
+                <a:ea typeface="Georgia"/>
               </a:rPr>
               <a:t>Styled Title Demo</a:t>
             </a:r>
@@ -615,7 +615,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{7F66C1B3-7761-414D-BD0A-34098D6C7DAA}">
+        <cx:series layoutId="boxWhisker" uniqueId="{8F48BE82-E013-456E-B466-558AB128BCB3}">
           <cx:tx>
             <cx:txData>
               <cx:f>1-Basics &amp; Quartile!$B$1</cx:f>
@@ -739,7 +739,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{1B414184-D429-4404-8DE9-46CF00651883}">
+        <cx:series layoutId="boxWhisker" uniqueId="{5C6DDC70-C31B-4C6E-B86E-65B944CF87FD}">
           <cx:tx>
             <cx:txData>
               <cx:f>1-Basics &amp; Quartile!$B$1</cx:f>
@@ -764,7 +764,7 @@
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{3EC803A6-9C8C-4A66-A2BB-2B8211B49455}">
+        <cx:series layoutId="boxWhisker" uniqueId="{D29B4928-367A-4536-A497-3E3437C508A5}">
           <cx:tx>
             <cx:txData>
               <cx:f>1-Basics &amp; Quartile!$C$1</cx:f>
@@ -912,7 +912,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{3D480C6F-2E0A-470C-BCFD-50AA5ABC1001}">
+        <cx:series layoutId="boxWhisker" uniqueId="{4E1572B0-D232-413F-84A1-2AD541B88E83}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Axes &amp; Styling!$B$1</cx:f>
@@ -925,7 +925,7 @@
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{6127D534-374C-4E9D-8966-20648B6FD639}">
+        <cx:series layoutId="boxWhisker" uniqueId="{55B1899F-8DE3-4A56-9D24-EBF521084A86}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Axes &amp; Styling!$C$1</cx:f>
@@ -1079,7 +1079,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{DF75A714-5514-4DB6-B1F6-CA468B47E88D}">
+        <cx:series layoutId="boxWhisker" uniqueId="{3ECB2130-7216-407E-89F4-BF95451A6659}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Axes &amp; Styling!$B$1</cx:f>
@@ -1193,7 +1193,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{592CB1B6-9BCC-4F87-A3A5-6BF299FEA71F}">
+        <cx:series layoutId="boxWhisker" uniqueId="{AE5DD002-E553-4626-9861-B31075053890}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Axes &amp; Styling!$B$1</cx:f>
@@ -1382,8 +1382,6 @@
                 <a:solidFill>
                   <a:srgbClr val="0F172A"/>
                 </a:solidFill>
-                <a:latin typeface="Helvetica Neue"/>
-                <a:ea typeface="Helvetica Neue"/>
                 <a:effectLst>
                   <a:outerShdw blurRad="50800" dist="25400" dir="2700000" algn="tl" rotWithShape="0">
                     <a:srgbClr val="000000">
@@ -1391,6 +1389,8 @@
                     </a:srgbClr>
                   </a:outerShdw>
                 </a:effectLst>
+                <a:latin typeface="Helvetica Neue"/>
+                <a:ea typeface="Helvetica Neue"/>
               </a:rPr>
               <a:t>Server Latency Dashboard</a:t>
             </a:r>
@@ -1400,7 +1400,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{19921A0A-F210-4308-95D4-733129E3E8B4}">
+        <cx:series layoutId="boxWhisker" uniqueId="{11220657-C852-4F71-9158-009AFEE6F3B4}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Axes &amp; Styling!$B$1</cx:f>
@@ -1429,7 +1429,7 @@
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{784E9993-1C87-4058-9638-D446F8C45504}">
+        <cx:series layoutId="boxWhisker" uniqueId="{FC58A545-FCE5-4B54-84E1-06F8E66738F1}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Axes &amp; Styling!$C$1</cx:f>
@@ -1458,7 +1458,7 @@
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{AB5C43A4-4EFA-4100-A150-D0DDBC97BA30}">
+        <cx:series layoutId="boxWhisker" uniqueId="{80AE2E89-5FE8-4614-95F2-5FB62777E043}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Axes &amp; Styling!$D$1</cx:f>
@@ -6069,6 +6069,115 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
@@ -6247,7 +6356,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6146797655084aa7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76d0093e193642f5"/>
 </x:worksheet>
 </file>
 
@@ -6441,6 +6550,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccd1ad934e2d42a4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d39d2aee00e4be0"/>
 </x:worksheet>
 </file>